--- a/data/sync_queues.xlsx
+++ b/data/sync_queues.xlsx
@@ -463,17 +463,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29737adc-0210-4af8-9bc0-9f4a3f1a34eb</t>
+          <t>6749a8e5-5e30-4928-a890-b788a0bd5c62</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>70cc38ba-b8a3-4c60-a280-b14d4accbcc0</t>
+          <t>5ef60b2f-1d0b-4123-84e0-0ded346a3279</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -482,14 +482,14 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1b912ae1-0865-4d03-9dbe-1c71be6b1b4a</t>
+          <t>22ce7dd6-ae74-4d2e-9af8-9d21d2217a95</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -499,33 +499,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>607649b5-67a4-40ac-a297-9ac59a9f01cb</t>
+          <t>20f54398-d53c-4161-859b-85fb6c9da1b8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8584c838-a164-44e6-8554-bf1e88006598</t>
+          <t>7b2426ed-ba0e-40e1-ac3d-689db68f9cba</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6cebdcd4-0031-4f79-aa8b-ab16dc6c0358</t>
+          <t>46ba1aeb-b184-4b4b-a2a6-9374de7968e5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ed97f5ae-7ced-4890-bd0b-1699869c9bc0</t>
+          <t>777b455e-6615-4fbc-85e6-b025985c5468</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>a23906e3-0846-4066-b9bd-e7d6a1b76f2d</t>
+          <t>4da48ce4-1c11-4658-a40d-c7fb8e5f7bd2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -564,24 +564,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>78bcec19-2e87-4cd2-bd7e-c34688b0f0bf</t>
+          <t>361294ca-2c93-4152-a192-9bc1765c26a2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3d24bb45-86a6-4a84-a311-ad820b7e3b3a</t>
+          <t>6b6cac21-9394-4212-917e-2deda0bb3137</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -597,7 +597,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7296e0a2-4972-41ca-be99-2206da57cd42</t>
+          <t>17cbf689-15c0-4230-8595-f9d6c879297b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,93 +607,85 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5f186f7c-978b-409b-8974-4aac8411c3e6</t>
+          <t>a8568320-8fc5-4b2f-b58c-0e0d4dadaedc</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>59000819-4f8e-4c9f-8526-902c72fb40ae</t>
+          <t>666c91cd-6814-47cc-b78d-89a439f52824</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>208375ac-bbda-4d62-a059-055b541d8aa8</t>
+          <t>6513b0bb-c4f8-48fe-9296-c1438c383dab</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9f55fa6c-154f-4135-bcfd-83ccedf9c243</t>
+          <t>691f5961-673d-4a2e-9c36-7cd9a2fd84f4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>00061644-75ae-4493-aca9-ad339cce972f</t>
+          <t>903e602b-427d-438d-be81-cee96261e16c</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>603b533b-c8d0-40a7-a1c2-943740816e83</t>
+          <t>399b5d85-72b5-4c74-95d8-a08a98131513</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>b264ff0a-6ed7-4b40-8967-a7f979378e1f</t>
+          <t>1fa3321d-1acd-4805-ac09-9c10b63c3ebc</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -709,93 +701,89 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>978f739c-583d-4214-8bea-64b67bae3d14</t>
+          <t>e6213d46-8c21-449b-8305-41fefd2e1b2d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>58d74b0e-6429-4bae-a45f-e6ef61721cc0</t>
+          <t>1494c849-bdaf-4e15-9714-cf7a5a514928</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Failed</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tally ODBC server unreachable.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>35d456d8-6224-407c-a10d-e9326d1ca594</t>
+          <t>4a7ce54a-a5ae-4d2a-b722-9763ffae6349</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>de1ecc61-394f-4f51-aa22-180493843b82</t>
+          <t>bdc6269a-b556-449e-885c-70bcd7d1b278</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>027cb894-e223-4551-a830-8e3d0789a54a</t>
+          <t>efba949b-3db6-43cf-9cfb-64d1ffef50bf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dc5334b7-e97f-4802-820e-5402993161d6</t>
+          <t>1a788923-5197-4777-af8e-bd188c910849</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cd9daf73-279f-4797-8ec6-d73131d16960</t>
+          <t>f048da03-c7d2-407b-8436-96b711c61fd8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -805,123 +793,115 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>df809089-a490-4630-b823-71882d246705</t>
+          <t>0e3ae05e-859c-44e5-afaa-fe7caf32a0f0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9d931c4b-3281-4d1e-8294-f8bf9b0afad6</t>
+          <t>97ab9287-5359-420c-addd-2269d514a454</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4b3ce142-627d-4abc-ae91-7235a50939f8</t>
+          <t>897ecd93-4dcc-4bda-a39c-334959f24d8f</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Failed</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tally ODBC server unreachable.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>c6dfb745-0661-4ea0-997b-281a24868223</t>
+          <t>1395279c-3af6-480f-a748-1753bdec550f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2d6c927c-0ef0-4cfc-ac68-1765d7a08365</t>
+          <t>abea692f-339e-4bae-9f8f-636930c4163c</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>a601d0c9-38f3-4703-96da-fd4c1e715bc8</t>
+          <t>183acaa5-1fdf-4532-b40f-56f1b9f44b2f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>b4705be8-7974-4afa-af0b-ab063ee34c8c</t>
+          <t>a96d319c-9940-4ca8-be69-c45246ff638f</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>951cb94c-9b55-4d61-86ed-8eab956704b4</t>
+          <t>0c432a24-b1bb-44ba-aa56-08d9b1f34212</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ad537c37-fb4e-4b8f-abc5-5a1ff30d25d4</t>
+          <t>087523f1-9c30-4305-a335-308e0e7ee8da</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -930,126 +910,122 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4af62441-6e2f-4932-9856-6ab18b1ee122</t>
+          <t>578adda0-f2da-48d3-9bde-25ba18f55bc3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>91f890b9-a419-40d4-ba70-990d0874b102</t>
+          <t>b2cdd2a0-eff6-44b4-b985-0641365bdb3c</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>77f852cc-3870-499a-bc37-624286d2adb3</t>
+          <t>ee4f2341-869d-4dab-88b7-d50017f49346</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>433c4c3b-ebca-4a8f-bf5e-9fe3fd118f0d</t>
+          <t>814d8a0f-6a5d-45e4-8738-d81f465a87d4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5ec529a9-4308-4d2c-9843-b1ec6a482af8</t>
+          <t>07f4465d-3c44-4023-be26-17859f679aaa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ad4d4eca-36bd-4108-bedd-901a3de761d5</t>
+          <t>1a4256bc-5f15-4f41-b8b6-156b0f80e58f</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>af6e1010-146b-4562-945e-b3db2be588bc</t>
+          <t>b4d3a58f-0694-4328-ac4a-12463ee88c38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>f3ebd335-e5e9-470a-9d66-fe1ed6aa5e59</t>
+          <t>410aa3fc-71e2-412e-bd2f-69bf9f1a20fa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Failed</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tally ODBC server unreachable.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9933e377-a5a6-4e5e-a006-f479d4a6066e</t>
+          <t>4f9c4569-eb53-4d25-8f96-49c3f9c3f4c5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1059,67 +1035,59 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3dce7eca-24c4-49c7-8ce7-731d3418c6d3</t>
+          <t>b5c79231-1593-4d4d-88a1-315831ea2f4f</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>65f7f66d-93bf-4965-87f1-cb135a3ce198</t>
+          <t>af26dd98-7abf-4a4b-b979-cb1f4551531d</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ad6e3d9e-3698-40fe-8670-132a2c827862</t>
+          <t>fb86bc4b-92b0-4e24-9106-b4f9f55eed78</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>23c0bd01-a2cb-4e17-bc26-8e69ad504f40</t>
+          <t>3bdf5d58-9bb1-4059-85f0-1eb28a0462c9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>c10139b0-4ecc-4aa6-838e-b7c022176d93</t>
+          <t>80c84ff5-ae9b-4233-b481-40e1cd79c628</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1139,22 +1107,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>c0d6c3ad-caa7-4e3f-bfe8-65b597085f19</t>
+          <t>f04d723c-cd64-41c7-a932-40ce0946c80a</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>b49ce5f8-91f5-4777-9f1c-686678f6aa7b</t>
+          <t>72130af5-2657-4e96-b570-4b12e1672d30</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1165,17 +1133,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1b1c4f40-4960-4a38-b6df-d42dedd90fb0</t>
+          <t>e903706c-1da0-437a-b63f-e8240e7d3de3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>14483a43-8c0b-4ae4-8f2d-01a856c659cf</t>
+          <t>52b89380-778f-49f5-a5ab-fc0304f78543</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1184,7 +1152,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1195,69 +1163,77 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>a21189c4-73a0-4954-bb9d-6ad914508981</t>
+          <t>4031c398-e167-41ba-9d94-3225bd6a1c73</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>348b571a-4baf-414f-9e3c-6cd66aaa92e8</t>
+          <t>8b5da9ec-0259-4f78-81b3-2ddec3ef1aeb</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Failed</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tally ODBC server unreachable.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>81ac9482-2ec2-400c-9be1-55cb0de98215</t>
+          <t>34c590d7-4ecd-480c-a61d-38f16d1a856d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0689799a-49a2-4842-8118-6c4cbfdbc889</t>
+          <t>4117e5c6-cb63-492d-8beb-c0b344366f32</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Failed</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tally ODBC server unreachable.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>21c86b1d-ba9d-492f-88bf-3c36f4cca4d9</t>
+          <t>55222696-15e5-45e5-b791-ab3a2d674666</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ec999fef-989f-4bb9-9b01-6db79d568585</t>
+          <t>75ab3b00-5e0e-44b8-aa2d-28fa2d703c92</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1266,14 +1242,14 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>81d3298b-7dcc-4d11-83cb-f81fdd909ac9</t>
+          <t>cab53a48-e5ed-439b-b521-6cf592383382</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1283,33 +1259,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>86bfb269-6c28-44b0-8b45-c4c2c726dd69</t>
+          <t>094a6727-2638-4d08-9481-a4b153167aa1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Failed</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tally ODBC server unreachable.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fbc422ca-579d-4084-a98c-09f8c9ba7751</t>
+          <t>9a657fc0-4b0e-4d70-bb19-0d6683c7618c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>92cd99a9-30e0-4707-9fe5-9f7c7e6474e0</t>
+          <t>18ca45c1-0703-404c-aa84-d6974fd15632</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1325,73 +1305,69 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>029ae534-1c7a-4e85-831f-ddc08db9a77a</t>
+          <t>d8c73f40-d8d9-4696-add6-ac7dde5390f9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5ae656af-2f94-41c4-8d99-ded7c4b8e76c</t>
+          <t>36c12236-e2b8-4285-aa9c-8302386cabb2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>a9feb98a-44b8-4a04-adb6-e1d3abb3dc2e</t>
+          <t>671bf15c-4bf1-457a-a211-50f5cf767a60</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7452ab2a-3ab5-46d1-9ec4-0d15de225346</t>
+          <t>1d8e4ae9-5f0d-4040-84a2-9136786e4af4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cb21388a-59db-4fc0-b375-02f06199f263</t>
+          <t>d263bc34-81b5-41db-9f4d-a1b445dab5c2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>51093859-6f91-4914-8a0e-4389c684aeb7</t>
+          <t>09a6fbd6-c99f-483a-9a29-f1e5009a051f</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1400,14 +1376,14 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0058ea7f-bc17-4d05-b8a9-eb3b03bb0e96</t>
+          <t>c4252b7d-24f1-4a5b-9cc1-fd8820823326</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1417,7 +1393,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>409fa375-fcf5-4f31-942d-d4e9600e0004</t>
+          <t>4589f900-457e-4dbe-aaa2-415ba5695fa6</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1426,7 +1402,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1437,7 +1413,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1baf9d42-137a-4c04-a4ec-36a89484647f</t>
+          <t>c6d0554e-5f75-449d-96de-e3edda4835eb</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1447,53 +1423,49 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ba62ba1b-041b-4ef0-926d-978fe5f77927</t>
+          <t>ffb41718-b588-4a85-a0c8-f77a23f97a9c</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06f9e67c-d210-4804-8e01-96a39553911e</t>
+          <t>7794f2fb-be4b-4a23-89d5-f88712648ce5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>b73ba737-b9ed-4f2e-b8dd-117fc8036162</t>
+          <t>68727f89-2f47-4391-a45e-b6718395c57f</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>33a55c26-669a-4f4c-af40-d09200c858d5</t>
+          <t>a30ed1fe-45b3-4356-af0c-45a82680fa1d</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1503,7 +1475,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>a3fce0d3-a537-4e62-84e8-4d86573e1540</t>
+          <t>9bfc6ec4-39b1-4683-b737-e647d2740de2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1512,14 +1484,14 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4ca7eff1-3400-4a4a-ac8c-b96bb21ac961</t>
+          <t>239b3b9b-961c-4ac5-b7e4-f63a90772b0c</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1529,33 +1501,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>21e92aa2-0c9d-4455-b26d-22a9914b0ff3</t>
+          <t>d757ad68-8eae-48d0-9c1f-c158ae06050a</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Failed</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tally ODBC server unreachable.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>afd5ef5c-09aa-4f99-9042-68eb7c62e692</t>
+          <t>bc5cba9e-92bb-4770-bc88-81622630beac</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>e5c22daa-ee5b-47fa-9905-71d62cb1d793</t>
+          <t>3a5ea924-fb7b-451f-aec5-704f97a448da</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1564,7 +1540,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1575,7 +1551,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7eba0aec-b9ea-4edc-8d63-f6b51b7b822f</t>
+          <t>38297134-b59b-4c02-949d-b432cce2fe7d</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1585,59 +1561,59 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4d936935-c79b-44a9-be5b-0fe124ce0813</t>
+          <t>1b98f64f-8b03-46e9-a382-8a018a1bcf34</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>326526bb-c4f7-45f5-ad44-9b0ca0cbef82</t>
+          <t>6630ab17-3107-422d-9bdd-4437a8ca6524</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>48378e23-94f8-444b-9862-c85e4aadc44d</t>
+          <t>6cdf36cc-cd7d-41b4-8f5d-d1253244b5f0</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>70225fde-a44e-4630-9fce-ea9ff36256cc</t>
+          <t>e58a13ff-4029-4af7-96cc-9b12de4199b9</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>06d8b53b-118f-4883-b33a-98d0b32df8b7</t>
+          <t>9380e49c-f2f3-4d5b-9a06-abe785bcc8e1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1646,7 +1622,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1657,99 +1633,99 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>b8a614cb-0abb-4d8a-a7ed-023c6cb6e3da</t>
+          <t>071c16df-99fb-4151-a51d-1b8cae786802</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>f7e4f665-efb0-45ea-8f6d-401686d79828</t>
+          <t>a76e1ac0-6003-4d8d-8c4c-a430c23d40d1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Tally ODBC server unreachable.</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cf031be1-dadc-4498-9d84-119e462a9154</t>
+          <t>52f5ac8e-6aeb-4105-b374-bbb4bf20b03c</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>86714354-5337-4238-a0a4-fbfb5ee194d1</t>
+          <t>44409c25-fd98-4a6a-a38b-f6612b5beafa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Failed</t>
         </is>
       </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tally ODBC server unreachable.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>324f0d34-9aad-469a-a12d-d248da0da67c</t>
+          <t>780c1f30-34f6-4751-b5cc-0967c117a049</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>634fcbdc-c05b-473f-b275-54e541ab1934</t>
+          <t>a59110be-0a3d-4c41-a05b-92daefd67392</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>d7a8280b-d7da-4368-9815-29dbad0b9415</t>
+          <t>c0e11aa6-83b3-462b-93e7-71c592ae0a85</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>e7105180-7e31-465f-b988-1bee3e652676</t>
+          <t>238d1678-6586-4388-8d71-dd16fe74ec0c</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1765,7 +1741,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>a16f1656-4ef2-4e8d-9c11-a037e7833759</t>
+          <t>c312a326-2353-491b-a049-c68226183de5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1775,68 +1751,68 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>7187655a-827e-49a1-af7b-8b2250131eea</t>
+          <t>6cd84f93-bc48-42fb-90b4-7cb4f6eb1bf6</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>e1b3f976-27db-4516-a684-5ae09a841fde</t>
+          <t>69023f33-f753-4d11-9cbd-445d415d9a96</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0a245c13-4c51-4c7a-ba8a-6ac97f8d6147</t>
+          <t>a482cb91-4f58-4cc8-866e-231a16ccac19</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>c2b83c0f-e35e-4f16-880b-93f3b142d8c0</t>
+          <t>f59480ba-2ebc-4466-9f13-9da4b1aaac7d</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>de0a900b-284a-4c33-8a65-ac0af5009d5b</t>
+          <t>773dc52a-c7ca-4f37-a584-1989002b35b3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="inlineStr"/>
     </row>
